--- a/artfynd/A 23682-2026 artfynd.xlsx
+++ b/artfynd/A 23682-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856804</v>
       </c>
       <c r="B2" t="n">
-        <v>102255</v>
+        <v>102261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23682-2026 artfynd.xlsx
+++ b/artfynd/A 23682-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856804</v>
       </c>
       <c r="B2" t="n">
-        <v>102261</v>
+        <v>102263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23682-2026 artfynd.xlsx
+++ b/artfynd/A 23682-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856804</v>
       </c>
       <c r="B2" t="n">
-        <v>102263</v>
+        <v>102291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133857252</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>133857168</v>
       </c>
       <c r="B4" t="n">
-        <v>57136</v>
+        <v>57143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>133857908</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23682-2026 artfynd.xlsx
+++ b/artfynd/A 23682-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856804</v>
       </c>
       <c r="B2" t="n">
-        <v>102291</v>
+        <v>102301</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133857252</v>
       </c>
       <c r="B3" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>133857168</v>
       </c>
       <c r="B4" t="n">
-        <v>57143</v>
+        <v>57153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>133857908</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23682-2026 artfynd.xlsx
+++ b/artfynd/A 23682-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856804</v>
       </c>
       <c r="B2" t="n">
-        <v>102301</v>
+        <v>102303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23682-2026 artfynd.xlsx
+++ b/artfynd/A 23682-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856804</v>
       </c>
       <c r="B2" t="n">
-        <v>102304</v>
+        <v>102311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23682-2026 artfynd.xlsx
+++ b/artfynd/A 23682-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133856804</v>
+        <v>133857252</v>
       </c>
       <c r="B2" t="n">
-        <v>102311</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långvasselbron, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490269</v>
+        <v>490361</v>
       </c>
       <c r="R2" t="n">
-        <v>6672162</v>
+        <v>6672027</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,14 +787,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133857252</v>
+        <v>133857908</v>
       </c>
       <c r="B3" t="n">
         <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -813,7 +818,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490361</v>
+        <v>490443</v>
       </c>
       <c r="R3" t="n">
-        <v>6672027</v>
+        <v>6671878</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,38 +899,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133857168</v>
+        <v>133858026</v>
       </c>
       <c r="B4" t="n">
-        <v>57153</v>
+        <v>57162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>dödad av predator</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490294</v>
+        <v>490481</v>
       </c>
       <c r="R4" t="n">
-        <v>6672132</v>
+        <v>6671852</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -969,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spridda dun i mossan vid spisröse. Predatordödad fågel?</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,27 +1011,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133857908</v>
+        <v>133857168</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>57153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1042,7 +1042,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>dödad av predator</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490443</v>
+        <v>490294</v>
       </c>
       <c r="R5" t="n">
-        <v>6671878</v>
+        <v>6672132</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spridda dun i mossan vid spisröse. Predatordödad fågel?</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,6 +1125,113 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133856804</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102318</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långvasselbron, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>490269</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6672162</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
